--- a/agricommodity_USA.xlsx
+++ b/agricommodity_USA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:W99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,6 +585,11 @@
           <t>Rice</t>
         </is>
       </c>
+      <c r="W4" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -610,6 +616,11 @@
       <c r="O5" t="n">
         <v>2.6</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -636,6 +647,11 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -662,6 +678,11 @@
       <c r="O7" t="n">
         <v>2.7</v>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -688,6 +709,11 @@
       <c r="O8" t="n">
         <v>2.7</v>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -714,6 +740,11 @@
       <c r="O9" t="n">
         <v>2.9</v>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -740,6 +771,11 @@
       <c r="O10" t="n">
         <v>2.8</v>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -766,6 +802,11 @@
       <c r="O11" t="n">
         <v>2.5</v>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -792,6 +833,11 @@
       <c r="O12" t="n">
         <v>2.5</v>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -818,6 +864,11 @@
       <c r="O13" t="n">
         <v>2.3</v>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -853,6 +904,11 @@
       <c r="O14" t="n">
         <v>2.4</v>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -888,6 +944,11 @@
       <c r="O15" t="n">
         <v>2.4</v>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -923,6 +984,11 @@
       <c r="O16" t="n">
         <v>2.6</v>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -958,6 +1024,11 @@
       <c r="O17" t="n">
         <v>2.6</v>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -993,6 +1064,11 @@
       <c r="O18" t="n">
         <v>3</v>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1028,6 +1104,11 @@
       <c r="O19" t="n">
         <v>3.4</v>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1063,6 +1144,11 @@
       <c r="O20" t="n">
         <v>4.3</v>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1098,6 +1184,11 @@
       <c r="O21" t="n">
         <v>4.8</v>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1133,6 +1224,11 @@
       <c r="O22" t="n">
         <v>3.8</v>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1168,6 +1264,11 @@
       <c r="O23" t="n">
         <v>3.4</v>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1203,6 +1304,11 @@
       <c r="O24" t="n">
         <v>3</v>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1238,6 +1344,11 @@
       <c r="O25" t="n">
         <v>2.9</v>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1273,6 +1384,11 @@
       <c r="O26" t="n">
         <v>3.2</v>
       </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1308,6 +1424,11 @@
       <c r="O27" t="n">
         <v>3.3</v>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1343,6 +1464,11 @@
       <c r="O28" t="n">
         <v>3</v>
       </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1384,6 +1510,11 @@
       <c r="P29" t="n">
         <v>7.1</v>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1425,6 +1556,11 @@
       <c r="P30" t="n">
         <v>6.8</v>
       </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1466,6 +1602,11 @@
       <c r="P31" t="n">
         <v>7</v>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1507,6 +1648,11 @@
       <c r="P32" t="n">
         <v>7.4</v>
       </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1548,6 +1694,11 @@
       <c r="P33" t="n">
         <v>6.9</v>
       </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1589,6 +1740,11 @@
       <c r="P34" t="n">
         <v>6.6</v>
       </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1630,6 +1786,11 @@
       <c r="P35" t="n">
         <v>6.7</v>
       </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1671,6 +1832,11 @@
       <c r="P36" t="n">
         <v>7.1</v>
       </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1712,6 +1878,11 @@
       <c r="P37" t="n">
         <v>7.3</v>
       </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1756,6 +1927,11 @@
       <c r="P38" t="n">
         <v>8</v>
       </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1800,6 +1976,11 @@
       <c r="P39" t="n">
         <v>8.699999999999999</v>
       </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1844,6 +2025,11 @@
       <c r="P40" t="n">
         <v>9.5</v>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1888,6 +2074,11 @@
       <c r="P41" t="n">
         <v>9</v>
       </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1932,6 +2123,11 @@
       <c r="P42" t="n">
         <v>8.6</v>
       </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1976,6 +2172,11 @@
       <c r="P43" t="n">
         <v>8.300000000000001</v>
       </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2020,6 +2221,11 @@
       <c r="P44" t="n">
         <v>8.300000000000001</v>
       </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2064,6 +2270,11 @@
       <c r="P45" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2108,6 +2319,11 @@
       <c r="P46" t="n">
         <v>10.2</v>
       </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2152,6 +2368,11 @@
       <c r="P47" t="n">
         <v>9.9</v>
       </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2202,6 +2423,11 @@
       <c r="V48" t="n">
         <v>1.7</v>
       </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2255,6 +2481,11 @@
       <c r="V49" t="n">
         <v>1.72</v>
       </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2308,6 +2539,11 @@
       <c r="V50" t="n">
         <v>1.68</v>
       </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2361,6 +2597,11 @@
       <c r="V51" t="n">
         <v>1.91</v>
       </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2414,6 +2655,11 @@
       <c r="V52" t="n">
         <v>1.87</v>
       </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2467,6 +2713,11 @@
       <c r="V53" t="n">
         <v>1.85</v>
       </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2520,6 +2771,11 @@
       <c r="V54" t="n">
         <v>1.62</v>
       </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2573,6 +2829,11 @@
       <c r="V55" t="n">
         <v>2.45</v>
       </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2626,6 +2887,11 @@
       <c r="V56" t="n">
         <v>4.04</v>
       </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2679,6 +2945,11 @@
       <c r="V57" t="n">
         <v>4.94</v>
       </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2732,6 +3003,11 @@
       <c r="V58" t="n">
         <v>5.09</v>
       </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2788,6 +3064,11 @@
       <c r="V59" t="n">
         <v>3.96</v>
       </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2844,6 +3125,11 @@
       <c r="V60" t="n">
         <v>2.07</v>
       </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2900,6 +3186,11 @@
       <c r="V61" t="n">
         <v>1.69</v>
       </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2956,6 +3247,11 @@
       <c r="V62" t="n">
         <v>1.98</v>
       </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3015,6 +3311,11 @@
       <c r="V63" t="n">
         <v>2.15</v>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3074,6 +3375,11 @@
       <c r="V64" t="n">
         <v>1.98</v>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3133,6 +3439,11 @@
       <c r="V65" t="n">
         <v>1.61</v>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3192,6 +3503,11 @@
       <c r="V66" t="n">
         <v>1.73</v>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3251,6 +3567,11 @@
       <c r="V67" t="n">
         <v>1.47</v>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3310,6 +3631,11 @@
       <c r="V68" t="n">
         <v>1.39</v>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3369,6 +3695,11 @@
       <c r="V69" t="n">
         <v>1.18</v>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3428,6 +3759,11 @@
       <c r="V70" t="n">
         <v>0.82</v>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3487,6 +3823,11 @@
       <c r="V71" t="n">
         <v>0.62</v>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3546,6 +3887,11 @@
       <c r="V72" t="n">
         <v>1</v>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3605,6 +3951,11 @@
       <c r="V73" t="n">
         <v>1.37</v>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3664,6 +4015,11 @@
       <c r="V74" t="n">
         <v>1.5</v>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3723,6 +4079,11 @@
       <c r="V75" t="n">
         <v>1.85</v>
       </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3782,6 +4143,11 @@
       <c r="V76" t="n">
         <v>1.63</v>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3841,6 +4207,11 @@
       <c r="V77" t="n">
         <v>1.25</v>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3900,6 +4271,11 @@
       <c r="V78" t="n">
         <v>1.3</v>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3959,6 +4335,11 @@
       <c r="V79" t="n">
         <v>1.35</v>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4018,6 +4399,11 @@
       <c r="V80" t="n">
         <v>1.85</v>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4077,6 +4463,11 @@
       <c r="V81" t="n">
         <v>2.24</v>
       </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4136,6 +4527,11 @@
       <c r="V82" t="n">
         <v>2.95</v>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4195,6 +4591,11 @@
       <c r="V83" t="n">
         <v>2.84</v>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4254,6 +4655,11 @@
       <c r="V84" t="n">
         <v>2.84</v>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4313,6 +4719,11 @@
       <c r="V85" t="n">
         <v>3.44</v>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4372,6 +4783,11 @@
       <c r="V86" t="n">
         <v>4.01</v>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4431,6 +4847,11 @@
       <c r="V87" t="n">
         <v>4.25</v>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4490,6 +4911,11 @@
       <c r="V88" t="n">
         <v>3.74</v>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4549,6 +4975,11 @@
       <c r="V89" t="n">
         <v>4.9</v>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4608,6 +5039,11 @@
       <c r="V90" t="n">
         <v>5.6</v>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4667,6 +5103,11 @@
       <c r="V91" t="n">
         <v>5.23</v>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4726,6 +5167,11 @@
       <c r="V92" t="n">
         <v>4.79</v>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4785,6 +5231,11 @@
       <c r="V93" t="n">
         <v>4.49</v>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4844,6 +5295,11 @@
       <c r="V94" t="n">
         <v>4.39</v>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4903,6 +5359,11 @@
       <c r="V95" t="n">
         <v>4.52</v>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4962,6 +5423,11 @@
       <c r="V96" t="n">
         <v>4.93</v>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5021,6 +5487,11 @@
       <c r="V97" t="n">
         <v>5</v>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5080,6 +5551,11 @@
       <c r="V98" t="n">
         <v>4.88</v>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5138,6 +5614,11 @@
       </c>
       <c r="V99" t="n">
         <v>5.03</v>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>USDA/NASS Prices Received by Farmers; HSUS Series K491-510</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5151,7 +5632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V103"/>
+  <dimension ref="A1:W103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5176,6 +5657,7 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5310,6 +5792,11 @@
           <t>Rice</t>
         </is>
       </c>
+      <c r="W4" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5330,6 +5817,11 @@
       <c r="T5" t="n">
         <v>14169.7</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>US Agricultural Census; HSUS Series K1-75</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5338,6 +5830,11 @@
       <c r="L6" t="n">
         <v>87.5</v>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5364,6 +5861,11 @@
       <c r="T7" t="n">
         <v>20380.1</v>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>US Agricultural Census; HSUS Series K1-75</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5393,6 +5895,11 @@
       <c r="T8" t="n">
         <v>29413.4</v>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>US Agricultural Census; HSUS Series K1-75</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5428,6 +5935,11 @@
       <c r="V9" t="n">
         <v>27.2</v>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5457,6 +5969,11 @@
       <c r="V10" t="n">
         <v>27.2</v>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5486,6 +6003,11 @@
       <c r="V11" t="n">
         <v>28.6</v>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5515,6 +6037,11 @@
       <c r="V12" t="n">
         <v>30.8</v>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5550,6 +6077,11 @@
       <c r="V13" t="n">
         <v>31.3</v>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5579,6 +6111,11 @@
       <c r="V14" t="n">
         <v>42.6</v>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5608,6 +6145,11 @@
       <c r="V15" t="n">
         <v>39.9</v>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5637,6 +6179,11 @@
       <c r="V16" t="n">
         <v>40.8</v>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5666,6 +6213,11 @@
       <c r="V17" t="n">
         <v>38.1</v>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5701,6 +6253,11 @@
       <c r="V18" t="n">
         <v>29.9</v>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5730,6 +6287,11 @@
       <c r="V19" t="n">
         <v>30.8</v>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5759,6 +6321,11 @@
       <c r="V20" t="n">
         <v>30.8</v>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5788,6 +6355,11 @@
       <c r="V21" t="n">
         <v>38.1</v>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5820,6 +6392,11 @@
       <c r="V22" t="n">
         <v>45.4</v>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5858,6 +6435,11 @@
       <c r="V23" t="n">
         <v>49.9</v>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5890,6 +6472,11 @@
       <c r="V24" t="n">
         <v>60.3</v>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5922,6 +6509,11 @@
       <c r="V25" t="n">
         <v>68</v>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5954,6 +6546,11 @@
       <c r="V26" t="n">
         <v>65.3</v>
       </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5986,6 +6583,11 @@
       <c r="V27" t="n">
         <v>74.8</v>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -6024,6 +6626,11 @@
       <c r="V28" t="n">
         <v>87.09999999999999</v>
       </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -6056,6 +6663,11 @@
       <c r="V29" t="n">
         <v>79.40000000000001</v>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -6088,6 +6700,11 @@
       <c r="V30" t="n">
         <v>82.59999999999999</v>
       </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -6120,6 +6737,11 @@
       <c r="V31" t="n">
         <v>86.59999999999999</v>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -6152,6 +6774,11 @@
       <c r="V32" t="n">
         <v>88.5</v>
       </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -6190,6 +6817,11 @@
       <c r="V33" t="n">
         <v>96.59999999999999</v>
       </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -6222,6 +6854,11 @@
       <c r="V34" t="n">
         <v>96.2</v>
       </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -6254,6 +6891,11 @@
       <c r="V35" t="n">
         <v>105.7</v>
       </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6286,6 +6928,11 @@
       <c r="V36" t="n">
         <v>109.8</v>
       </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6318,6 +6965,11 @@
       <c r="V37" t="n">
         <v>120.7</v>
       </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6356,6 +7008,11 @@
       <c r="V38" t="n">
         <v>138.3</v>
       </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6388,6 +7045,11 @@
       <c r="V39" t="n">
         <v>126.1</v>
       </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6420,6 +7082,11 @@
       <c r="V40" t="n">
         <v>152.9</v>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6452,6 +7119,11 @@
       <c r="V41" t="n">
         <v>144.2</v>
       </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6484,6 +7156,11 @@
       <c r="V42" t="n">
         <v>137</v>
       </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6522,6 +7199,11 @@
       <c r="V43" t="n">
         <v>153.3</v>
       </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6554,6 +7236,11 @@
       <c r="V44" t="n">
         <v>149.7</v>
       </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6586,6 +7273,11 @@
       <c r="V45" t="n">
         <v>151</v>
       </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6618,6 +7310,11 @@
       <c r="V46" t="n">
         <v>166.5</v>
       </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6650,6 +7347,11 @@
       <c r="V47" t="n">
         <v>160.1</v>
       </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6688,6 +7390,11 @@
       <c r="V48" t="n">
         <v>198.2</v>
       </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6726,6 +7433,11 @@
       <c r="V49" t="n">
         <v>201.4</v>
       </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6764,6 +7476,11 @@
       <c r="V50" t="n">
         <v>207.7</v>
       </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6802,6 +7519,11 @@
       <c r="V51" t="n">
         <v>234.5</v>
       </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6861,6 +7583,11 @@
       <c r="V52" t="n">
         <v>250.8</v>
       </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6920,6 +7647,11 @@
       <c r="V53" t="n">
         <v>269.4</v>
       </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6979,6 +7711,11 @@
       <c r="V54" t="n">
         <v>251.3</v>
       </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7038,6 +7775,11 @@
       <c r="V55" t="n">
         <v>283.5</v>
       </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7097,6 +7839,11 @@
       <c r="V56" t="n">
         <v>272.2</v>
       </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7156,6 +7903,11 @@
       <c r="V57" t="n">
         <v>294.8</v>
       </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7215,6 +7967,11 @@
       <c r="V58" t="n">
         <v>322.1</v>
       </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7274,6 +8031,11 @@
       <c r="V59" t="n">
         <v>267.6</v>
       </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7333,6 +8095,11 @@
       <c r="V60" t="n">
         <v>291.7</v>
       </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7392,6 +8159,11 @@
       <c r="V61" t="n">
         <v>334.3</v>
       </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7451,6 +8223,11 @@
       <c r="V62" t="n">
         <v>367.9</v>
       </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7516,6 +8293,11 @@
       <c r="V63" t="n">
         <v>360.6</v>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7581,6 +8363,11 @@
       <c r="V64" t="n">
         <v>355.6</v>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7646,6 +8433,11 @@
       <c r="V65" t="n">
         <v>382.4</v>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7711,6 +8503,11 @@
       <c r="V66" t="n">
         <v>370.1</v>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7776,6 +8573,11 @@
       <c r="V67" t="n">
         <v>388.3</v>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7841,6 +8643,11 @@
       <c r="V68" t="n">
         <v>363.3</v>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7906,6 +8713,11 @@
       <c r="V69" t="n">
         <v>377.8</v>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7971,6 +8783,11 @@
       <c r="V70" t="n">
         <v>390.5</v>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8036,6 +8853,11 @@
       <c r="V71" t="n">
         <v>396.4</v>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8101,6 +8923,11 @@
       <c r="V72" t="n">
         <v>406.4</v>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8166,6 +8993,11 @@
       <c r="V73" t="n">
         <v>401.4</v>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8231,6 +9063,11 @@
       <c r="V74" t="n">
         <v>403.7</v>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8296,6 +9133,11 @@
       <c r="V75" t="n">
         <v>411</v>
       </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8361,6 +9203,11 @@
       <c r="V76" t="n">
         <v>347.5</v>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8426,6 +9273,11 @@
       <c r="V77" t="n">
         <v>346.6</v>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8491,6 +9343,11 @@
       <c r="V78" t="n">
         <v>383.3</v>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8556,6 +9413,11 @@
       <c r="V79" t="n">
         <v>379.7</v>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8621,6 +9483,11 @@
       <c r="V80" t="n">
         <v>435.9</v>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8686,6 +9553,11 @@
       <c r="V81" t="n">
         <v>464.9</v>
       </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8751,6 +9623,11 @@
       <c r="V82" t="n">
         <v>456.3</v>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8816,6 +9693,11 @@
       <c r="V83" t="n">
         <v>520.3</v>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8881,6 +9763,11 @@
       <c r="V84" t="n">
         <v>548.4</v>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8946,6 +9833,11 @@
       <c r="V85" t="n">
         <v>562</v>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9011,6 +9903,11 @@
       <c r="V86" t="n">
         <v>557</v>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9076,6 +9973,11 @@
       <c r="V87" t="n">
         <v>600.6</v>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9141,6 +10043,11 @@
       <c r="V88" t="n">
         <v>610.1</v>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9206,6 +10113,11 @@
       <c r="V89" t="n">
         <v>644.1</v>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9271,6 +10183,11 @@
       <c r="V90" t="n">
         <v>650.5</v>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9336,6 +10253,11 @@
       <c r="V91" t="n">
         <v>708.5</v>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9401,6 +10323,11 @@
       <c r="V92" t="n">
         <v>668.6</v>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9466,6 +10393,11 @@
       <c r="V93" t="n">
         <v>705.3</v>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9531,6 +10463,11 @@
       <c r="V94" t="n">
         <v>699.5</v>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9596,6 +10533,11 @@
       <c r="V95" t="n">
         <v>751.6</v>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9661,6 +10603,11 @@
       <c r="V96" t="n">
         <v>741.2</v>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9726,6 +10673,11 @@
       <c r="V97" t="n">
         <v>752.1</v>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9791,6 +10743,11 @@
       <c r="V98" t="n">
         <v>840.1</v>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -9856,6 +10813,11 @@
       <c r="V99" t="n">
         <v>811</v>
       </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9921,6 +10883,11 @@
       <c r="V100" t="n">
         <v>831.4</v>
       </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9986,6 +10953,11 @@
       <c r="V101" t="n">
         <v>901.8</v>
       </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10051,6 +11023,11 @@
       <c r="V102" t="n">
         <v>892.7</v>
       </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10115,6 +11092,11 @@
       </c>
       <c r="V103" t="n">
         <v>959.8</v>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>USDA/NASS; HSUS Series K1-75, K507-522; USDA Agricultural Statistics</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -10128,7 +11110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V144"/>
+  <dimension ref="A1:W144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10153,6 +11135,7 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10287,6 +11270,11 @@
           <t>Rice</t>
         </is>
       </c>
+      <c r="W4" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -10295,6 +11283,11 @@
       <c r="H5" t="n">
         <v>54.4</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -10303,6 +11296,11 @@
       <c r="H6" t="n">
         <v>59</v>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -10311,6 +11309,11 @@
       <c r="H7" t="n">
         <v>57.2</v>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10319,6 +11322,11 @@
       <c r="H8" t="n">
         <v>63.5</v>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10327,6 +11335,11 @@
       <c r="H9" t="n">
         <v>67.09999999999999</v>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10335,6 +11348,11 @@
       <c r="H10" t="n">
         <v>72.59999999999999</v>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10343,6 +11361,11 @@
       <c r="H11" t="n">
         <v>77.09999999999999</v>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10351,6 +11374,11 @@
       <c r="H12" t="n">
         <v>79.8</v>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10359,6 +11387,11 @@
       <c r="H13" t="n">
         <v>82.59999999999999</v>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10367,6 +11400,11 @@
       <c r="H14" t="n">
         <v>85.3</v>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10375,6 +11413,11 @@
       <c r="H15" t="n">
         <v>90.7</v>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10383,6 +11426,11 @@
       <c r="H16" t="n">
         <v>96.2</v>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10391,6 +11439,11 @@
       <c r="H17" t="n">
         <v>99.8</v>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10399,6 +11452,11 @@
       <c r="H18" t="n">
         <v>104.3</v>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10407,6 +11465,11 @@
       <c r="H19" t="n">
         <v>108.9</v>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10415,6 +11478,11 @@
       <c r="H20" t="n">
         <v>113.4</v>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10423,6 +11491,11 @@
       <c r="H21" t="n">
         <v>104.3</v>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10431,6 +11504,11 @@
       <c r="H22" t="n">
         <v>108.9</v>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10439,6 +11517,11 @@
       <c r="H23" t="n">
         <v>113.4</v>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10447,6 +11530,11 @@
       <c r="H24" t="n">
         <v>131.5</v>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -10455,6 +11543,11 @@
       <c r="H25" t="n">
         <v>140.6</v>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -10463,6 +11556,11 @@
       <c r="H26" t="n">
         <v>125.2</v>
       </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -10471,6 +11569,11 @@
       <c r="H27" t="n">
         <v>142.4</v>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -10479,6 +11582,11 @@
       <c r="H28" t="n">
         <v>158.8</v>
       </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -10487,6 +11595,11 @@
       <c r="H29" t="n">
         <v>172.4</v>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -10495,6 +11608,11 @@
       <c r="H30" t="n">
         <v>170.6</v>
       </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -10503,6 +11621,11 @@
       <c r="H31" t="n">
         <v>176.9</v>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -10511,6 +11634,11 @@
       <c r="H32" t="n">
         <v>190.5</v>
       </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -10519,6 +11647,11 @@
       <c r="H33" t="n">
         <v>199.6</v>
       </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -10527,6 +11660,11 @@
       <c r="H34" t="n">
         <v>228.6</v>
       </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -10535,6 +11673,11 @@
       <c r="H35" t="n">
         <v>249.5</v>
       </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -10543,6 +11686,11 @@
       <c r="H36" t="n">
         <v>264.9</v>
       </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -10551,6 +11699,11 @@
       <c r="H37" t="n">
         <v>290.3</v>
       </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -10559,6 +11712,11 @@
       <c r="H38" t="n">
         <v>308.4</v>
       </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -10567,6 +11725,11 @@
       <c r="H39" t="n">
         <v>294.8</v>
       </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -10575,6 +11738,11 @@
       <c r="H40" t="n">
         <v>333.8</v>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -10583,6 +11751,11 @@
       <c r="H41" t="n">
         <v>353.8</v>
       </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -10591,6 +11764,11 @@
       <c r="H42" t="n">
         <v>308.4</v>
       </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -10599,6 +11777,11 @@
       <c r="H43" t="n">
         <v>331.1</v>
       </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -10610,6 +11793,11 @@
       <c r="K44" t="n">
         <v>1.1</v>
       </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -10618,6 +11806,11 @@
       <c r="H45" t="n">
         <v>263.1</v>
       </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -10626,6 +11819,11 @@
       <c r="H46" t="n">
         <v>230.4</v>
       </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -10634,6 +11832,11 @@
       <c r="H47" t="n">
         <v>252.2</v>
       </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -10642,6 +11845,11 @@
       <c r="H48" t="n">
         <v>273.1</v>
       </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -10650,6 +11858,11 @@
       <c r="H49" t="n">
         <v>283</v>
       </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -10658,6 +11871,11 @@
       <c r="H50" t="n">
         <v>413.7</v>
       </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -10666,6 +11884,11 @@
       <c r="H51" t="n">
         <v>443.6</v>
       </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -10674,6 +11897,11 @@
       <c r="H52" t="n">
         <v>464.5</v>
       </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -10682,6 +11910,11 @@
       <c r="H53" t="n">
         <v>484.4</v>
       </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -10699,6 +11932,11 @@
       <c r="Q54" t="n">
         <v>5</v>
       </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -10710,6 +11948,11 @@
       <c r="Q55" t="n">
         <v>6</v>
       </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -10721,6 +11964,11 @@
       <c r="Q56" t="n">
         <v>7</v>
       </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -10732,6 +11980,11 @@
       <c r="Q57" t="n">
         <v>8</v>
       </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -10743,6 +11996,11 @@
       <c r="Q58" t="n">
         <v>7</v>
       </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -10757,6 +12015,11 @@
       <c r="Q59" t="n">
         <v>6</v>
       </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -10768,6 +12031,11 @@
       <c r="Q60" t="n">
         <v>7</v>
       </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -10779,6 +12047,11 @@
       <c r="Q61" t="n">
         <v>8</v>
       </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -10790,6 +12063,11 @@
       <c r="Q62" t="n">
         <v>7</v>
       </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -10801,6 +12079,11 @@
       <c r="Q63" t="n">
         <v>8</v>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -10821,6 +12104,11 @@
       <c r="S64" t="n">
         <v>2</v>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -10832,6 +12120,11 @@
       <c r="Q65" t="n">
         <v>11</v>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -10843,6 +12136,11 @@
       <c r="Q66" t="n">
         <v>12</v>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10854,6 +12152,11 @@
       <c r="Q67" t="n">
         <v>13</v>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10865,6 +12168,11 @@
       <c r="Q68" t="n">
         <v>12</v>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10882,6 +12190,11 @@
       <c r="S69" t="n">
         <v>3</v>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10893,6 +12206,11 @@
       <c r="Q70" t="n">
         <v>12</v>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10904,6 +12222,11 @@
       <c r="Q71" t="n">
         <v>13</v>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10915,6 +12238,11 @@
       <c r="Q72" t="n">
         <v>14</v>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10926,6 +12254,11 @@
       <c r="Q73" t="n">
         <v>13</v>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10946,6 +12279,11 @@
       <c r="S74" t="n">
         <v>5</v>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10957,6 +12295,11 @@
       <c r="Q75" t="n">
         <v>15</v>
       </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10968,6 +12311,11 @@
       <c r="Q76" t="n">
         <v>16</v>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10979,6 +12327,11 @@
       <c r="Q77" t="n">
         <v>15</v>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10990,6 +12343,11 @@
       <c r="Q78" t="n">
         <v>14</v>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11007,6 +12365,11 @@
       <c r="S79" t="n">
         <v>8</v>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11018,6 +12381,11 @@
       <c r="Q80" t="n">
         <v>12</v>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11029,6 +12397,11 @@
       <c r="Q81" t="n">
         <v>13</v>
       </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11040,6 +12413,11 @@
       <c r="Q82" t="n">
         <v>14</v>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11051,6 +12429,11 @@
       <c r="Q83" t="n">
         <v>15</v>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11101,6 +12484,11 @@
       <c r="V84" t="n">
         <v>10</v>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11148,6 +12536,11 @@
       <c r="V85" t="n">
         <v>12</v>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11195,6 +12588,11 @@
       <c r="V86" t="n">
         <v>15</v>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11242,6 +12640,11 @@
       <c r="V87" t="n">
         <v>12</v>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11289,6 +12692,11 @@
       <c r="V88" t="n">
         <v>10</v>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11339,6 +12747,11 @@
       <c r="V89" t="n">
         <v>12</v>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11389,6 +12802,11 @@
       <c r="V90" t="n">
         <v>10</v>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11439,6 +12857,11 @@
       <c r="V91" t="n">
         <v>8</v>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11489,6 +12912,11 @@
       <c r="V92" t="n">
         <v>10</v>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11539,6 +12967,11 @@
       <c r="V93" t="n">
         <v>12</v>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11589,6 +13022,11 @@
       <c r="V94" t="n">
         <v>10</v>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11639,6 +13077,11 @@
       <c r="V95" t="n">
         <v>8</v>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11689,6 +13132,11 @@
       <c r="V96" t="n">
         <v>10</v>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11739,6 +13187,11 @@
       <c r="V97" t="n">
         <v>12</v>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11789,6 +13242,11 @@
       <c r="V98" t="n">
         <v>10</v>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11839,6 +13297,11 @@
       <c r="V99" t="n">
         <v>8</v>
       </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11889,6 +13352,11 @@
       <c r="V100" t="n">
         <v>10</v>
       </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11939,6 +13407,11 @@
       <c r="V101" t="n">
         <v>12</v>
       </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11989,6 +13462,11 @@
       <c r="V102" t="n">
         <v>15</v>
       </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12039,6 +13517,11 @@
       <c r="V103" t="n">
         <v>12</v>
       </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12104,6 +13587,11 @@
       <c r="V104" t="n">
         <v>10</v>
       </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12166,6 +13654,11 @@
       <c r="V105" t="n">
         <v>12</v>
       </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12228,6 +13721,11 @@
       <c r="V106" t="n">
         <v>10</v>
       </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12290,6 +13788,11 @@
       <c r="V107" t="n">
         <v>8</v>
       </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12352,6 +13855,11 @@
       <c r="V108" t="n">
         <v>10</v>
       </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12414,6 +13922,11 @@
       <c r="V109" t="n">
         <v>12</v>
       </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12476,6 +13989,11 @@
       <c r="V110" t="n">
         <v>10</v>
       </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12538,6 +14056,11 @@
       <c r="V111" t="n">
         <v>8</v>
       </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12600,6 +14123,11 @@
       <c r="V112" t="n">
         <v>10</v>
       </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12662,6 +14190,11 @@
       <c r="V113" t="n">
         <v>12</v>
       </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12724,6 +14257,11 @@
       <c r="V114" t="n">
         <v>10</v>
       </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12786,6 +14324,11 @@
       <c r="V115" t="n">
         <v>8</v>
       </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12848,6 +14391,11 @@
       <c r="V116" t="n">
         <v>6</v>
       </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12913,6 +14461,11 @@
       <c r="V117" t="n">
         <v>8</v>
       </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12978,6 +14531,11 @@
       <c r="V118" t="n">
         <v>10</v>
       </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13043,6 +14601,11 @@
       <c r="V119" t="n">
         <v>8</v>
       </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13108,6 +14671,11 @@
       <c r="V120" t="n">
         <v>10</v>
       </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13173,6 +14741,11 @@
       <c r="V121" t="n">
         <v>12</v>
       </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13238,6 +14811,11 @@
       <c r="V122" t="n">
         <v>10</v>
       </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13303,6 +14881,11 @@
       <c r="V123" t="n">
         <v>8</v>
       </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13371,6 +14954,11 @@
       <c r="V124" t="n">
         <v>10</v>
       </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13439,6 +15027,11 @@
       <c r="V125" t="n">
         <v>12</v>
       </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13507,6 +15100,11 @@
       <c r="V126" t="n">
         <v>10</v>
       </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13575,6 +15173,11 @@
       <c r="V127" t="n">
         <v>8</v>
       </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13643,6 +15246,11 @@
       <c r="V128" t="n">
         <v>10</v>
       </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13711,6 +15319,11 @@
       <c r="V129" t="n">
         <v>12</v>
       </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13779,6 +15392,11 @@
       <c r="V130" t="n">
         <v>10</v>
       </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13847,6 +15465,11 @@
       <c r="V131" t="n">
         <v>8</v>
       </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13915,6 +15538,11 @@
       <c r="V132" t="n">
         <v>10</v>
       </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13983,6 +15611,11 @@
       <c r="V133" t="n">
         <v>12</v>
       </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14051,6 +15684,11 @@
       <c r="V134" t="n">
         <v>15</v>
       </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14119,6 +15757,11 @@
       <c r="V135" t="n">
         <v>12</v>
       </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14187,6 +15830,11 @@
       <c r="V136" t="n">
         <v>10</v>
       </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14255,6 +15903,11 @@
       <c r="V137" t="n">
         <v>12</v>
       </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14323,6 +15976,11 @@
       <c r="V138" t="n">
         <v>10</v>
       </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14391,6 +16049,11 @@
       <c r="V139" t="n">
         <v>8</v>
       </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14459,6 +16122,11 @@
       <c r="V140" t="n">
         <v>10</v>
       </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14527,6 +16195,11 @@
       <c r="V141" t="n">
         <v>12</v>
       </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14595,6 +16268,11 @@
       <c r="V142" t="n">
         <v>10</v>
       </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14663,6 +16341,11 @@
       <c r="V143" t="n">
         <v>8</v>
       </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14730,6 +16413,11 @@
       </c>
       <c r="V144" t="n">
         <v>10</v>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -14743,7 +16431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V144"/>
+  <dimension ref="A1:W144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14768,6 +16456,7 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14902,6 +16591,11 @@
           <t>Rice</t>
         </is>
       </c>
+      <c r="W4" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -14910,6 +16604,11 @@
       <c r="H5" t="n">
         <v>2520</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -14918,6 +16617,11 @@
       <c r="H6" t="n">
         <v>2665</v>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -14926,6 +16630,11 @@
       <c r="H7" t="n">
         <v>2394</v>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14934,6 +16643,11 @@
       <c r="H8" t="n">
         <v>2590</v>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14942,6 +16656,11 @@
       <c r="H9" t="n">
         <v>2590</v>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14950,6 +16669,11 @@
       <c r="H10" t="n">
         <v>2720</v>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14958,6 +16682,11 @@
       <c r="H11" t="n">
         <v>2805</v>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14966,6 +16695,11 @@
       <c r="H12" t="n">
         <v>2816</v>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14974,6 +16708,11 @@
       <c r="H13" t="n">
         <v>2821</v>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14982,6 +16721,11 @@
       <c r="H14" t="n">
         <v>2820</v>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14990,6 +16734,11 @@
       <c r="H15" t="n">
         <v>2800</v>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14998,6 +16747,11 @@
       <c r="H16" t="n">
         <v>2862</v>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15006,6 +16760,11 @@
       <c r="H17" t="n">
         <v>3080</v>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15014,6 +16773,11 @@
       <c r="H18" t="n">
         <v>3105</v>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15022,6 +16786,11 @@
       <c r="H19" t="n">
         <v>3360</v>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15030,6 +16799,11 @@
       <c r="H20" t="n">
         <v>3750</v>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15038,6 +16812,11 @@
       <c r="H21" t="n">
         <v>3680</v>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15046,6 +16825,11 @@
       <c r="H22" t="n">
         <v>3360</v>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15054,6 +16838,11 @@
       <c r="H23" t="n">
         <v>3625</v>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15062,6 +16851,11 @@
       <c r="H24" t="n">
         <v>4060</v>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -15070,6 +16864,11 @@
       <c r="H25" t="n">
         <v>4030</v>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -15078,6 +16877,11 @@
       <c r="H26" t="n">
         <v>3036</v>
       </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -15086,6 +16890,11 @@
       <c r="H27" t="n">
         <v>3140</v>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15094,6 +16903,11 @@
       <c r="H28" t="n">
         <v>3675</v>
       </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15102,6 +16916,11 @@
       <c r="H29" t="n">
         <v>4180</v>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -15110,6 +16929,11 @@
       <c r="H30" t="n">
         <v>4136</v>
       </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -15118,6 +16942,11 @@
       <c r="H31" t="n">
         <v>4680</v>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -15126,6 +16955,11 @@
       <c r="H32" t="n">
         <v>4620</v>
       </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -15134,6 +16968,11 @@
       <c r="H33" t="n">
         <v>4400</v>
       </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -15142,6 +16981,11 @@
       <c r="H34" t="n">
         <v>5544</v>
       </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -15150,6 +16994,11 @@
       <c r="H35" t="n">
         <v>6600</v>
       </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -15158,6 +17007,11 @@
       <c r="H36" t="n">
         <v>7008</v>
       </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -15166,6 +17020,11 @@
       <c r="H37" t="n">
         <v>8320</v>
       </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -15174,6 +17033,11 @@
       <c r="H38" t="n">
         <v>9520</v>
       </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -15182,6 +17046,11 @@
       <c r="H39" t="n">
         <v>9750</v>
       </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -15190,6 +17059,11 @@
       <c r="H40" t="n">
         <v>11776</v>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -15198,6 +17072,11 @@
       <c r="H41" t="n">
         <v>13260</v>
       </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -15206,6 +17085,11 @@
       <c r="H42" t="n">
         <v>10200</v>
       </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -15214,6 +17098,11 @@
       <c r="H43" t="n">
         <v>11680</v>
       </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -15222,6 +17111,11 @@
       <c r="H44" t="n">
         <v>13804</v>
       </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -15230,6 +17124,11 @@
       <c r="H45" t="n">
         <v>9280</v>
       </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -15238,6 +17137,11 @@
       <c r="H46" t="n">
         <v>9652</v>
       </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -15246,6 +17150,11 @@
       <c r="H47" t="n">
         <v>11676</v>
       </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -15254,6 +17163,11 @@
       <c r="H48" t="n">
         <v>15652</v>
       </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -15262,6 +17176,11 @@
       <c r="H49" t="n">
         <v>14976</v>
       </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -15270,6 +17189,11 @@
       <c r="H50" t="n">
         <v>20064</v>
       </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -15278,6 +17202,11 @@
       <c r="H51" t="n">
         <v>20538</v>
       </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -15286,6 +17215,11 @@
       <c r="H52" t="n">
         <v>20480</v>
       </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -15294,6 +17228,11 @@
       <c r="H53" t="n">
         <v>20292</v>
       </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -15305,6 +17244,11 @@
       <c r="Q54" t="n">
         <v>2500</v>
       </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -15316,6 +17260,11 @@
       <c r="Q55" t="n">
         <v>3000</v>
       </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -15327,6 +17276,11 @@
       <c r="Q56" t="n">
         <v>3500</v>
       </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -15338,6 +17292,11 @@
       <c r="Q57" t="n">
         <v>4000</v>
       </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -15349,6 +17308,11 @@
       <c r="Q58" t="n">
         <v>3500</v>
       </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -15363,6 +17327,11 @@
       <c r="Q59" t="n">
         <v>3000</v>
       </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -15374,6 +17343,11 @@
       <c r="Q60" t="n">
         <v>3500</v>
       </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -15385,6 +17359,11 @@
       <c r="Q61" t="n">
         <v>4000</v>
       </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -15396,6 +17375,11 @@
       <c r="Q62" t="n">
         <v>3500</v>
       </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -15407,6 +17391,11 @@
       <c r="Q63" t="n">
         <v>4000</v>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -15421,6 +17410,11 @@
       <c r="Q64" t="n">
         <v>5000</v>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -15432,6 +17426,11 @@
       <c r="Q65" t="n">
         <v>5500</v>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -15443,6 +17442,11 @@
       <c r="Q66" t="n">
         <v>6000</v>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -15454,6 +17458,11 @@
       <c r="Q67" t="n">
         <v>6500</v>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -15465,6 +17474,11 @@
       <c r="Q68" t="n">
         <v>6000</v>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -15479,6 +17493,11 @@
       <c r="Q69" t="n">
         <v>5500</v>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -15490,6 +17509,11 @@
       <c r="Q70" t="n">
         <v>6000</v>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -15501,6 +17525,11 @@
       <c r="Q71" t="n">
         <v>6500</v>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -15512,6 +17541,11 @@
       <c r="Q72" t="n">
         <v>7000</v>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -15523,6 +17557,11 @@
       <c r="Q73" t="n">
         <v>6500</v>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -15540,6 +17579,11 @@
       <c r="Q74" t="n">
         <v>7000</v>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -15551,6 +17595,11 @@
       <c r="Q75" t="n">
         <v>7500</v>
       </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -15562,6 +17611,11 @@
       <c r="Q76" t="n">
         <v>8000</v>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -15573,6 +17627,11 @@
       <c r="Q77" t="n">
         <v>7500</v>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -15584,6 +17643,11 @@
       <c r="Q78" t="n">
         <v>7000</v>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -15598,6 +17662,11 @@
       <c r="Q79" t="n">
         <v>6500</v>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -15609,6 +17678,11 @@
       <c r="Q80" t="n">
         <v>6000</v>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -15620,6 +17694,11 @@
       <c r="Q81" t="n">
         <v>6500</v>
       </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -15631,6 +17710,11 @@
       <c r="Q82" t="n">
         <v>7000</v>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -15642,6 +17726,11 @@
       <c r="Q83" t="n">
         <v>7500</v>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -15680,6 +17769,11 @@
       <c r="Q84" t="n">
         <v>8000</v>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -15715,6 +17809,11 @@
       <c r="Q85" t="n">
         <v>8500</v>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -15750,6 +17849,11 @@
       <c r="Q86" t="n">
         <v>9000</v>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -15785,6 +17889,11 @@
       <c r="Q87" t="n">
         <v>9500</v>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -15820,6 +17929,11 @@
       <c r="Q88" t="n">
         <v>10000</v>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -15858,6 +17972,11 @@
       <c r="Q89" t="n">
         <v>10500</v>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -15896,6 +18015,11 @@
       <c r="Q90" t="n">
         <v>11000</v>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -15934,6 +18058,11 @@
       <c r="Q91" t="n">
         <v>11500</v>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -15972,6 +18101,11 @@
       <c r="Q92" t="n">
         <v>11000</v>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -16016,6 +18150,11 @@
       <c r="V93" t="n">
         <v>450</v>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -16060,6 +18199,11 @@
       <c r="V94" t="n">
         <v>379</v>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -16104,6 +18248,11 @@
       <c r="V95" t="n">
         <v>296</v>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -16148,6 +18297,11 @@
       <c r="V96" t="n">
         <v>421</v>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -16192,6 +18346,11 @@
       <c r="V97" t="n">
         <v>495</v>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -16236,6 +18395,11 @@
       <c r="V98" t="n">
         <v>408</v>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -16280,6 +18444,11 @@
       <c r="V99" t="n">
         <v>286</v>
       </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -16324,6 +18493,11 @@
       <c r="V100" t="n">
         <v>540</v>
       </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -16368,6 +18542,11 @@
       <c r="V101" t="n">
         <v>1069</v>
       </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -16412,6 +18591,11 @@
       <c r="V102" t="n">
         <v>1634</v>
       </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -16456,6 +18640,11 @@
       <c r="V103" t="n">
         <v>1347</v>
       </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -16512,6 +18701,11 @@
       <c r="V104" t="n">
         <v>873</v>
       </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -16565,6 +18759,11 @@
       <c r="V105" t="n">
         <v>548</v>
       </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -16618,6 +18817,11 @@
       <c r="V106" t="n">
         <v>373</v>
       </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -16671,6 +18875,11 @@
       <c r="V107" t="n">
         <v>349</v>
       </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -16727,6 +18936,11 @@
       <c r="V108" t="n">
         <v>474</v>
       </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -16783,6 +18997,11 @@
       <c r="V109" t="n">
         <v>524</v>
       </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -16839,6 +19058,11 @@
       <c r="V110" t="n">
         <v>355</v>
       </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -16895,6 +19119,11 @@
       <c r="V111" t="n">
         <v>305</v>
       </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -16951,6 +19180,11 @@
       <c r="V112" t="n">
         <v>324</v>
       </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -17007,6 +19241,11 @@
       <c r="V113" t="n">
         <v>368</v>
       </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -17063,6 +19302,11 @@
       <c r="V114" t="n">
         <v>260</v>
       </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -17119,6 +19363,11 @@
       <c r="V115" t="n">
         <v>145</v>
       </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -17175,6 +19424,11 @@
       <c r="V116" t="n">
         <v>82</v>
       </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -17234,6 +19488,11 @@
       <c r="V117" t="n">
         <v>176</v>
       </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -17293,6 +19552,11 @@
       <c r="V118" t="n">
         <v>302</v>
       </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -17352,6 +19616,11 @@
       <c r="V119" t="n">
         <v>265</v>
       </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -17411,6 +19680,11 @@
       <c r="V120" t="n">
         <v>408</v>
       </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -17470,6 +19744,11 @@
       <c r="V121" t="n">
         <v>431</v>
       </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -17529,6 +19808,11 @@
       <c r="V122" t="n">
         <v>276</v>
       </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -17588,6 +19872,11 @@
       <c r="V123" t="n">
         <v>229</v>
       </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -17650,6 +19939,11 @@
       <c r="V124" t="n">
         <v>298</v>
       </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17712,6 +20006,11 @@
       <c r="V125" t="n">
         <v>489</v>
       </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17774,6 +20073,11 @@
       <c r="V126" t="n">
         <v>494</v>
       </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -17836,6 +20140,11 @@
       <c r="V127" t="n">
         <v>520</v>
       </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -17898,6 +20207,11 @@
       <c r="V128" t="n">
         <v>626</v>
       </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17960,6 +20274,11 @@
       <c r="V129" t="n">
         <v>751</v>
       </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -18022,6 +20341,11 @@
       <c r="V130" t="n">
         <v>758</v>
       </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -18084,6 +20408,11 @@
       <c r="V131" t="n">
         <v>707</v>
       </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -18146,6 +20475,11 @@
       <c r="V132" t="n">
         <v>937</v>
       </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -18208,6 +20542,11 @@
       <c r="V133" t="n">
         <v>989</v>
       </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -18270,6 +20609,11 @@
       <c r="V134" t="n">
         <v>1620</v>
       </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -18332,6 +20676,11 @@
       <c r="V135" t="n">
         <v>1482</v>
       </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -18394,6 +20743,11 @@
       <c r="V136" t="n">
         <v>1153</v>
       </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18456,6 +20810,11 @@
       <c r="V137" t="n">
         <v>1267</v>
       </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18518,6 +20877,11 @@
       <c r="V138" t="n">
         <v>990</v>
       </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -18580,6 +20944,11 @@
       <c r="V139" t="n">
         <v>774</v>
       </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -18642,6 +21011,11 @@
       <c r="V140" t="n">
         <v>996</v>
       </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -18704,6 +21078,11 @@
       <c r="V141" t="n">
         <v>1304</v>
       </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -18766,6 +21145,11 @@
       <c r="V142" t="n">
         <v>1102</v>
       </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -18828,6 +21212,11 @@
       <c r="V143" t="n">
         <v>861</v>
       </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -18889,6 +21278,11 @@
       </c>
       <c r="V144" t="n">
         <v>1109</v>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × price</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -18902,7 +21296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V144"/>
+  <dimension ref="A1:W144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18927,6 +21321,7 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19061,6 +21456,11 @@
           <t>Rice</t>
         </is>
       </c>
+      <c r="W4" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -19072,6 +21472,11 @@
       <c r="U5" t="n">
         <v>15.9</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -19083,6 +21488,11 @@
       <c r="U6" t="n">
         <v>19.1</v>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -19094,6 +21504,11 @@
       <c r="U7" t="n">
         <v>20.4</v>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -19105,6 +21520,11 @@
       <c r="U8" t="n">
         <v>22.7</v>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -19116,6 +21536,11 @@
       <c r="U9" t="n">
         <v>24.9</v>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -19127,6 +21552,11 @@
       <c r="U10" t="n">
         <v>27.2</v>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -19138,6 +21568,11 @@
       <c r="U11" t="n">
         <v>29.5</v>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -19149,6 +21584,11 @@
       <c r="U12" t="n">
         <v>31.8</v>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -19160,6 +21600,11 @@
       <c r="U13" t="n">
         <v>32.7</v>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -19171,6 +21616,11 @@
       <c r="U14" t="n">
         <v>34</v>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -19182,6 +21632,11 @@
       <c r="U15" t="n">
         <v>36.3</v>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -19193,6 +21648,11 @@
       <c r="U16" t="n">
         <v>38.6</v>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -19204,6 +21664,11 @@
       <c r="U17" t="n">
         <v>40.8</v>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -19215,6 +21680,11 @@
       <c r="U18" t="n">
         <v>43.1</v>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19226,6 +21696,11 @@
       <c r="U19" t="n">
         <v>45.4</v>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19237,6 +21712,11 @@
       <c r="U20" t="n">
         <v>47.6</v>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19248,6 +21728,11 @@
       <c r="U21" t="n">
         <v>45.4</v>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19259,6 +21744,11 @@
       <c r="U22" t="n">
         <v>49.9</v>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19270,6 +21760,11 @@
       <c r="U23" t="n">
         <v>54.4</v>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19287,6 +21782,11 @@
       <c r="U24" t="n">
         <v>59</v>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -19304,6 +21804,11 @@
       <c r="U25" t="n">
         <v>61.2</v>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -19321,6 +21826,11 @@
       <c r="U26" t="n">
         <v>59</v>
       </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -19338,6 +21848,11 @@
       <c r="U27" t="n">
         <v>61.2</v>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -19355,6 +21870,11 @@
       <c r="U28" t="n">
         <v>65.8</v>
       </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -19372,6 +21892,11 @@
       <c r="U29" t="n">
         <v>70.3</v>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -19389,6 +21914,11 @@
       <c r="U30" t="n">
         <v>72.59999999999999</v>
       </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -19406,6 +21936,11 @@
       <c r="U31" t="n">
         <v>79.40000000000001</v>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -19423,6 +21958,11 @@
       <c r="U32" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -19440,6 +21980,11 @@
       <c r="U33" t="n">
         <v>86.2</v>
       </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -19457,6 +22002,11 @@
       <c r="U34" t="n">
         <v>90.7</v>
       </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -19477,6 +22027,11 @@
       <c r="U35" t="n">
         <v>99.8</v>
       </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -19497,6 +22052,11 @@
       <c r="U36" t="n">
         <v>106.6</v>
       </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -19517,6 +22077,11 @@
       <c r="U37" t="n">
         <v>113.4</v>
       </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -19537,6 +22102,11 @@
       <c r="U38" t="n">
         <v>122.5</v>
       </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -19557,6 +22127,11 @@
       <c r="U39" t="n">
         <v>127</v>
       </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -19577,6 +22152,11 @@
       <c r="U40" t="n">
         <v>136.1</v>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -19597,6 +22177,11 @@
       <c r="U41" t="n">
         <v>145.2</v>
       </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -19617,6 +22202,11 @@
       <c r="U42" t="n">
         <v>140.6</v>
       </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -19637,6 +22227,11 @@
       <c r="U43" t="n">
         <v>149.7</v>
       </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -19657,6 +22252,11 @@
       <c r="U44" t="n">
         <v>158.8</v>
       </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -19677,6 +22277,11 @@
       <c r="U45" t="n">
         <v>154.2</v>
       </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -19697,6 +22302,11 @@
       <c r="U46" t="n">
         <v>163.3</v>
       </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -19717,6 +22327,11 @@
       <c r="U47" t="n">
         <v>172.4</v>
       </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -19737,6 +22352,11 @@
       <c r="U48" t="n">
         <v>158.8</v>
       </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -19757,6 +22377,11 @@
       <c r="U49" t="n">
         <v>163.3</v>
       </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -19777,6 +22402,11 @@
       <c r="U50" t="n">
         <v>181.4</v>
       </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -19797,6 +22427,11 @@
       <c r="U51" t="n">
         <v>195</v>
       </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -19817,6 +22452,11 @@
       <c r="U52" t="n">
         <v>204.1</v>
       </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -19837,6 +22477,11 @@
       <c r="U53" t="n">
         <v>217.7</v>
       </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -19875,6 +22520,11 @@
       <c r="V54" t="n">
         <v>3.6</v>
       </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -19910,6 +22560,11 @@
       <c r="V55" t="n">
         <v>4.5</v>
       </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -19945,6 +22600,11 @@
       <c r="V56" t="n">
         <v>5.4</v>
       </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -19980,6 +22640,11 @@
       <c r="V57" t="n">
         <v>6.8</v>
       </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -20015,6 +22680,11 @@
       <c r="V58" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -20053,6 +22723,11 @@
       <c r="V59" t="n">
         <v>9.1</v>
       </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -20088,6 +22763,11 @@
       <c r="V60" t="n">
         <v>10</v>
       </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -20123,6 +22803,11 @@
       <c r="V61" t="n">
         <v>11.3</v>
       </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -20158,6 +22843,11 @@
       <c r="V62" t="n">
         <v>12.7</v>
       </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -20193,6 +22883,11 @@
       <c r="V63" t="n">
         <v>13.6</v>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -20231,6 +22926,11 @@
       <c r="V64" t="n">
         <v>15.9</v>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -20266,6 +22966,11 @@
       <c r="V65" t="n">
         <v>17.2</v>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -20301,6 +23006,11 @@
       <c r="V66" t="n">
         <v>18.1</v>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -20336,6 +23046,11 @@
       <c r="V67" t="n">
         <v>19.1</v>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -20371,6 +23086,11 @@
       <c r="V68" t="n">
         <v>20.4</v>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -20409,6 +23129,11 @@
       <c r="V69" t="n">
         <v>21.8</v>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -20444,6 +23169,11 @@
       <c r="V70" t="n">
         <v>22.7</v>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -20479,6 +23209,11 @@
       <c r="V71" t="n">
         <v>23.6</v>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -20514,6 +23249,11 @@
       <c r="V72" t="n">
         <v>24.9</v>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -20549,6 +23289,11 @@
       <c r="V73" t="n">
         <v>26.3</v>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -20587,6 +23332,11 @@
       <c r="V74" t="n">
         <v>27.2</v>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -20622,6 +23372,11 @@
       <c r="V75" t="n">
         <v>28.1</v>
       </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -20657,6 +23412,11 @@
       <c r="V76" t="n">
         <v>29.5</v>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -20692,6 +23452,11 @@
       <c r="V77" t="n">
         <v>30.8</v>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -20727,6 +23492,11 @@
       <c r="V78" t="n">
         <v>31.8</v>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -20765,6 +23535,11 @@
       <c r="V79" t="n">
         <v>34</v>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -20800,6 +23575,11 @@
       <c r="V80" t="n">
         <v>36.3</v>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -20835,6 +23615,11 @@
       <c r="V81" t="n">
         <v>38.6</v>
       </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -20870,6 +23655,11 @@
       <c r="V82" t="n">
         <v>40.8</v>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -20905,6 +23695,11 @@
       <c r="V83" t="n">
         <v>43.1</v>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -20964,6 +23759,11 @@
       <c r="V84" t="n">
         <v>45.4</v>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -21023,6 +23823,11 @@
       <c r="V85" t="n">
         <v>49.9</v>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -21082,6 +23887,11 @@
       <c r="V86" t="n">
         <v>54.4</v>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -21141,6 +23951,11 @@
       <c r="V87" t="n">
         <v>59</v>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -21200,6 +24015,11 @@
       <c r="V88" t="n">
         <v>54.4</v>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -21259,6 +24079,11 @@
       <c r="V89" t="n">
         <v>63.5</v>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -21318,6 +24143,11 @@
       <c r="V90" t="n">
         <v>68</v>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -21377,6 +24207,11 @@
       <c r="V91" t="n">
         <v>72.59999999999999</v>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -21436,6 +24271,11 @@
       <c r="V92" t="n">
         <v>77.09999999999999</v>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -21498,6 +24338,11 @@
       <c r="V93" t="n">
         <v>81.59999999999999</v>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -21560,6 +24405,11 @@
       <c r="V94" t="n">
         <v>90.7</v>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -21622,6 +24472,11 @@
       <c r="V95" t="n">
         <v>86.2</v>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -21684,6 +24539,11 @@
       <c r="V96" t="n">
         <v>95.3</v>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -21746,6 +24606,11 @@
       <c r="V97" t="n">
         <v>99.8</v>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -21808,6 +24673,11 @@
       <c r="V98" t="n">
         <v>113.4</v>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -21870,6 +24740,11 @@
       <c r="V99" t="n">
         <v>127</v>
       </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -21932,6 +24807,11 @@
       <c r="V100" t="n">
         <v>117.9</v>
       </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -21994,6 +24874,11 @@
       <c r="V101" t="n">
         <v>136.1</v>
       </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -22056,6 +24941,11 @@
       <c r="V102" t="n">
         <v>158.8</v>
       </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -22118,6 +25008,11 @@
       <c r="V103" t="n">
         <v>172.4</v>
       </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -22186,6 +25081,11 @@
       <c r="V104" t="n">
         <v>158.8</v>
       </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -22251,6 +25151,11 @@
       <c r="V105" t="n">
         <v>136.1</v>
       </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -22316,6 +25221,11 @@
       <c r="V106" t="n">
         <v>145.2</v>
       </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -22381,6 +25291,11 @@
       <c r="V107" t="n">
         <v>158.8</v>
       </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -22446,6 +25361,11 @@
       <c r="V108" t="n">
         <v>172.4</v>
       </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -22511,6 +25431,11 @@
       <c r="V109" t="n">
         <v>158.8</v>
       </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -22576,6 +25501,11 @@
       <c r="V110" t="n">
         <v>145.2</v>
       </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -22641,6 +25571,11 @@
       <c r="V111" t="n">
         <v>158.8</v>
       </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -22706,6 +25641,11 @@
       <c r="V112" t="n">
         <v>172.4</v>
       </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -22771,6 +25711,11 @@
       <c r="V113" t="n">
         <v>181.4</v>
       </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -22836,6 +25781,11 @@
       <c r="V114" t="n">
         <v>158.8</v>
       </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -22901,6 +25851,11 @@
       <c r="V115" t="n">
         <v>136.1</v>
       </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -22966,6 +25921,11 @@
       <c r="V116" t="n">
         <v>113.4</v>
       </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -23034,6 +25994,11 @@
       <c r="V117" t="n">
         <v>127</v>
       </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -23102,6 +26067,11 @@
       <c r="V118" t="n">
         <v>136.1</v>
       </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -23170,6 +26140,11 @@
       <c r="V119" t="n">
         <v>145.2</v>
       </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -23238,6 +26213,11 @@
       <c r="V120" t="n">
         <v>158.8</v>
       </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -23306,6 +26286,11 @@
       <c r="V121" t="n">
         <v>172.4</v>
       </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -23374,6 +26359,11 @@
       <c r="V122" t="n">
         <v>181.4</v>
       </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -23442,6 +26432,11 @@
       <c r="V123" t="n">
         <v>190.5</v>
       </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -23510,6 +26505,11 @@
       <c r="V124" t="n">
         <v>204.1</v>
       </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -23578,6 +26578,11 @@
       <c r="V125" t="n">
         <v>226.8</v>
       </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -23646,6 +26651,11 @@
       <c r="V126" t="n">
         <v>217.7</v>
       </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -23714,6 +26724,11 @@
       <c r="V127" t="n">
         <v>181.4</v>
       </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -23782,6 +26797,11 @@
       <c r="V128" t="n">
         <v>204.1</v>
       </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -23850,6 +26870,11 @@
       <c r="V129" t="n">
         <v>226.8</v>
       </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -23918,6 +26943,11 @@
       <c r="V130" t="n">
         <v>272.2</v>
       </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -23986,6 +27016,11 @@
       <c r="V131" t="n">
         <v>294.8</v>
       </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -24054,6 +27089,11 @@
       <c r="V132" t="n">
         <v>317.5</v>
       </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -24122,6 +27162,11 @@
       <c r="V133" t="n">
         <v>308.4</v>
       </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -24190,6 +27235,11 @@
       <c r="V134" t="n">
         <v>326.6</v>
       </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -24258,6 +27308,11 @@
       <c r="V135" t="n">
         <v>340.2</v>
       </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -24326,6 +27381,11 @@
       <c r="V136" t="n">
         <v>353.8</v>
       </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -24394,6 +27454,11 @@
       <c r="V137" t="n">
         <v>362.9</v>
       </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -24462,6 +27527,11 @@
       <c r="V138" t="n">
         <v>385.6</v>
       </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -24530,6 +27600,11 @@
       <c r="V139" t="n">
         <v>408.2</v>
       </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -24598,6 +27673,11 @@
       <c r="V140" t="n">
         <v>430.9</v>
       </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -24666,6 +27746,11 @@
       <c r="V141" t="n">
         <v>453.6</v>
       </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -24734,6 +27819,11 @@
       <c r="V142" t="n">
         <v>476.3</v>
       </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -24802,6 +27892,11 @@
       <c r="V143" t="n">
         <v>499</v>
       </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -24869,6 +27964,11 @@
       </c>
       <c r="V144" t="n">
         <v>521.6</v>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>HSUS Series U (Trade); USDA/FAS; US Bureau of Statistics</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -24882,7 +27982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V144"/>
+  <dimension ref="A1:W144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -24907,6 +28007,7 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25041,231 +28142,461 @@
           <t>Rice</t>
         </is>
       </c>
+      <c r="W4" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>1821</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>1822</v>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>1823</v>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>1824</v>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>1825</v>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>1826</v>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>1827</v>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>1828</v>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>1829</v>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>1830</v>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>1831</v>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>1832</v>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>1833</v>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>1834</v>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>1835</v>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>1836</v>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>1837</v>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>1838</v>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>1839</v>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>1840</v>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>1841</v>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>1842</v>
       </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>1843</v>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>1844</v>
       </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>1845</v>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>1846</v>
       </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>1847</v>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>1848</v>
       </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>1849</v>
       </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>1850</v>
       </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>1851</v>
       </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>1852</v>
       </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>1853</v>
       </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>1854</v>
       </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>1855</v>
       </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>1856</v>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>1857</v>
       </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>1858</v>
       </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>1859</v>
       </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>1860</v>
       </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>1861</v>
       </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>1862</v>
       </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>1863</v>
       </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>1864</v>
       </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>1865</v>
       </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -25280,6 +28611,11 @@
       <c r="N50" t="n">
         <v>14800</v>
       </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -25294,6 +28630,11 @@
       <c r="N51" t="n">
         <v>20640</v>
       </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -25308,6 +28649,11 @@
       <c r="N52" t="n">
         <v>21150</v>
       </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -25322,6 +28668,11 @@
       <c r="N53" t="n">
         <v>23040</v>
       </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -25342,6 +28693,11 @@
       <c r="N54" t="n">
         <v>21840</v>
       </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -25362,6 +28718,11 @@
       <c r="N55" t="n">
         <v>19440</v>
       </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -25382,6 +28743,11 @@
       <c r="N56" t="n">
         <v>24360</v>
       </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -25402,6 +28768,11 @@
       <c r="N57" t="n">
         <v>28200</v>
       </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -25422,6 +28793,11 @@
       <c r="N58" t="n">
         <v>27520</v>
       </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -25451,6 +28827,11 @@
       <c r="N59" t="n">
         <v>25160</v>
       </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -25477,6 +28858,11 @@
       <c r="N60" t="n">
         <v>23800</v>
       </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -25503,6 +28889,11 @@
       <c r="N61" t="n">
         <v>30340</v>
       </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -25529,6 +28920,11 @@
       <c r="N62" t="n">
         <v>30400</v>
       </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -25555,6 +28951,11 @@
       <c r="N63" t="n">
         <v>36120</v>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -25584,6 +28985,11 @@
       <c r="N64" t="n">
         <v>43700</v>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -25610,6 +29016,11 @@
       <c r="N65" t="n">
         <v>50000</v>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -25636,6 +29047,11 @@
       <c r="N66" t="n">
         <v>63800</v>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -25662,6 +29078,11 @@
       <c r="N67" t="n">
         <v>47150</v>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -25688,6 +29109,11 @@
       <c r="N68" t="n">
         <v>45600</v>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -25717,6 +29143,11 @@
       <c r="N69" t="n">
         <v>48750</v>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -25743,6 +29174,11 @@
       <c r="N70" t="n">
         <v>49400</v>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -25769,6 +29205,11 @@
       <c r="N71" t="n">
         <v>58050</v>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -25795,6 +29236,11 @@
       <c r="N72" t="n">
         <v>65800</v>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -25821,6 +29267,11 @@
       <c r="N73" t="n">
         <v>53650</v>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -25850,6 +29301,11 @@
       <c r="N74" t="n">
         <v>60000</v>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -25876,6 +29332,11 @@
       <c r="N75" t="n">
         <v>73600</v>
       </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -25902,6 +29363,11 @@
       <c r="N76" t="n">
         <v>79900</v>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -25928,6 +29394,11 @@
       <c r="N77" t="n">
         <v>80500</v>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -25954,6 +29425,11 @@
       <c r="N78" t="n">
         <v>77400</v>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -25983,6 +29459,11 @@
       <c r="N79" t="n">
         <v>70300</v>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -26009,6 +29490,11 @@
       <c r="N80" t="n">
         <v>66500</v>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -26035,6 +29521,11 @@
       <c r="N81" t="n">
         <v>62400</v>
       </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -26061,6 +29552,11 @@
       <c r="N82" t="n">
         <v>72000</v>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -26087,6 +29583,11 @@
       <c r="N83" t="n">
         <v>86100</v>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -26134,6 +29635,11 @@
       <c r="Q84" t="n">
         <v>250</v>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -26181,6 +29687,11 @@
       <c r="Q85" t="n">
         <v>300</v>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -26228,6 +29739,11 @@
       <c r="Q86" t="n">
         <v>400</v>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -26275,6 +29791,11 @@
       <c r="Q87" t="n">
         <v>300</v>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -26322,6 +29843,11 @@
       <c r="Q88" t="n">
         <v>250</v>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -26369,6 +29895,11 @@
       <c r="Q89" t="n">
         <v>300</v>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -26416,6 +29947,11 @@
       <c r="Q90" t="n">
         <v>250</v>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -26463,6 +29999,11 @@
       <c r="Q91" t="n">
         <v>200</v>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -26510,6 +30051,11 @@
       <c r="Q92" t="n">
         <v>250</v>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -26563,6 +30109,11 @@
       <c r="V93" t="n">
         <v>3060</v>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -26619,6 +30170,11 @@
       <c r="V94" t="n">
         <v>3440</v>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -26675,6 +30231,11 @@
       <c r="V95" t="n">
         <v>3192</v>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -26731,6 +30292,11 @@
       <c r="V96" t="n">
         <v>4011</v>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -26787,6 +30353,11 @@
       <c r="V97" t="n">
         <v>4114</v>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -26843,6 +30414,11 @@
       <c r="V98" t="n">
         <v>4625</v>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -26899,6 +30475,11 @@
       <c r="V99" t="n">
         <v>4536</v>
       </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -26955,6 +30536,11 @@
       <c r="V100" t="n">
         <v>6370</v>
       </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -27011,6 +30597,11 @@
       <c r="V101" t="n">
         <v>12120</v>
       </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -27067,6 +30658,11 @@
       <c r="V102" t="n">
         <v>17290</v>
       </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -27123,6 +30719,11 @@
       <c r="V103" t="n">
         <v>19342</v>
       </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -27182,6 +30783,11 @@
       <c r="V104" t="n">
         <v>13860</v>
       </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -27238,6 +30844,11 @@
       <c r="V105" t="n">
         <v>6210</v>
       </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -27294,6 +30905,11 @@
       <c r="V106" t="n">
         <v>5408</v>
       </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -27350,6 +30966,11 @@
       <c r="V107" t="n">
         <v>6930</v>
       </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -27409,6 +31030,11 @@
       <c r="V108" t="n">
         <v>8170</v>
       </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -27468,6 +31094,11 @@
       <c r="V109" t="n">
         <v>6930</v>
       </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -27527,6 +31158,11 @@
       <c r="V110" t="n">
         <v>5152</v>
       </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -27586,6 +31222,11 @@
       <c r="V111" t="n">
         <v>6055</v>
       </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -27645,6 +31286,11 @@
       <c r="V112" t="n">
         <v>5586</v>
       </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -27704,6 +31350,11 @@
       <c r="V113" t="n">
         <v>5560</v>
       </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -27763,6 +31414,11 @@
       <c r="V114" t="n">
         <v>4130</v>
       </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -27822,6 +31478,11 @@
       <c r="V115" t="n">
         <v>2460</v>
       </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -27881,6 +31542,11 @@
       <c r="V116" t="n">
         <v>1550</v>
       </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -27943,6 +31609,11 @@
       <c r="V117" t="n">
         <v>2800</v>
       </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -28005,6 +31676,11 @@
       <c r="V118" t="n">
         <v>4110</v>
       </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -28067,6 +31743,11 @@
       <c r="V119" t="n">
         <v>4800</v>
       </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -28129,6 +31810,11 @@
       <c r="V120" t="n">
         <v>6475</v>
       </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -28191,6 +31877,11 @@
       <c r="V121" t="n">
         <v>6194</v>
       </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -28253,6 +31944,11 @@
       <c r="V122" t="n">
         <v>5000</v>
       </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -28315,6 +32011,11 @@
       <c r="V123" t="n">
         <v>5460</v>
       </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -28377,6 +32078,11 @@
       <c r="V124" t="n">
         <v>6075</v>
       </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -28439,6 +32145,11 @@
       <c r="V125" t="n">
         <v>9250</v>
       </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -28501,6 +32212,11 @@
       <c r="V126" t="n">
         <v>10752</v>
       </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -28563,6 +32279,11 @@
       <c r="V127" t="n">
         <v>11800</v>
       </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -28625,6 +32346,11 @@
       <c r="V128" t="n">
         <v>12780</v>
       </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -28687,6 +32413,11 @@
       <c r="V129" t="n">
         <v>14200</v>
       </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -28749,6 +32480,11 @@
       <c r="V130" t="n">
         <v>20640</v>
       </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -28811,6 +32547,11 @@
       <c r="V131" t="n">
         <v>26065</v>
       </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -28873,6 +32614,11 @@
       <c r="V132" t="n">
         <v>29750</v>
       </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -28935,6 +32681,11 @@
       <c r="V133" t="n">
         <v>25432</v>
       </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -28997,6 +32748,11 @@
       <c r="V134" t="n">
         <v>35280</v>
       </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -29059,6 +32815,11 @@
       <c r="V135" t="n">
         <v>42000</v>
       </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -29121,6 +32882,11 @@
       <c r="V136" t="n">
         <v>40794</v>
       </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -29183,6 +32949,11 @@
       <c r="V137" t="n">
         <v>38320</v>
       </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -29245,6 +33016,11 @@
       <c r="V138" t="n">
         <v>38165</v>
       </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -29307,6 +33083,11 @@
       <c r="V139" t="n">
         <v>39510</v>
       </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -29369,6 +33150,11 @@
       <c r="V140" t="n">
         <v>42940</v>
       </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -29431,6 +33217,11 @@
       <c r="V141" t="n">
         <v>49300</v>
       </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -29493,6 +33284,11 @@
       <c r="V142" t="n">
         <v>52500</v>
       </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -29555,6 +33351,11 @@
       <c r="V143" t="n">
         <v>53680</v>
       </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -29616,6 +33417,11 @@
       </c>
       <c r="V144" t="n">
         <v>57845</v>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>HSUS Series U; USDA/FAS; estimated from quantity × farm price</t>
+        </is>
       </c>
     </row>
   </sheetData>
